--- a/excel_routes/route_CCE_GIZ_threats.xlsx
+++ b/excel_routes/route_CCE_GIZ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -537,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9245</v>
+        <v>8651</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9315</v>
+        <v>8891</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-70</v>
+        <v>-240</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-APR-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9245</v>
+        <v>8651</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9315</v>
+        <v>8891</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-70</v>
+        <v>-240</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,12 +622,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-329</t>
+          <t>SM-983</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -627,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9245</v>
+        <v>7552</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9806</v>
+        <v>8285</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-561</v>
+        <v>-733</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -672,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9245</v>
+        <v>8651</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9806</v>
+        <v>8891</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-561</v>
+        <v>-240</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8376</v>
+        <v>12427</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>9090</v>
+        <v>13019</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-714</v>
+        <v>-592</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8376</v>
+        <v>11244</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>9090</v>
+        <v>11342</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-714</v>
+        <v>-98</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -807,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7701</v>
+        <v>11835</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7730</v>
+        <v>12314</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-29</v>
+        <v>-479</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -852,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7701</v>
+        <v>9271</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7730</v>
+        <v>10356</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-29</v>
+        <v>-1085</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -897,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7701</v>
+        <v>9637</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7730</v>
+        <v>10821</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-29</v>
+        <v>-1184</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>18-APR-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -942,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7701</v>
+        <v>9271</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7730</v>
+        <v>9651</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-29</v>
+        <v>-380</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -987,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8291</v>
+        <v>9637</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9090</v>
+        <v>9863</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-799</v>
+        <v>-226</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1032,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8291</v>
+        <v>9271</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9090</v>
+        <v>9863</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-799</v>
+        <v>-592</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8376</v>
+        <v>10116</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9090</v>
+        <v>10356</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-714</v>
+        <v>-240</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1108,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8376</v>
+        <v>10624</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9090</v>
+        <v>10821</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-714</v>
+        <v>-197</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1153,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1167,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10591</v>
+        <v>10116</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10774</v>
+        <v>10356</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-183</v>
+        <v>-240</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1198,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1212,13 +1221,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10591</v>
+        <v>10624</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10774</v>
+        <v>10821</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-183</v>
+        <v>-197</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1243,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1257,26 +1266,26 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9477</v>
+        <v>9866</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10269</v>
+        <v>15668</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-792</v>
+        <v>-5802</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1288,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1298,17 +1307,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9477</v>
+        <v>10116</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10269</v>
+        <v>15668</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-792</v>
+        <v>-5552</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1319,12 +1328,1632 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-4565</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-4565</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>11103</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-4565</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>12371</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-3297</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>12371</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-3297</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>12427</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-3241</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>12794</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-2874</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>13216</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-2452</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-585</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>9866</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-5802</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>12794</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-2874</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>12794</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-2874</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>12794</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-2874</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>12427</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-3241</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>13075</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-2593</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>05-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>11244</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-4424</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-4284</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-4284</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>10116</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-5552</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-4284</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-4284</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>10116</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-5552</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>12-SEP-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>10116</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-5552</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-4284</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-4284</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>10116</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-5552</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-754</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>19-SEP-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>11807</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>10116</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>10821</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-705</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>26-SEP-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-141</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>10116</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>10356</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-240</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CCE_GIZ_threats.xlsx
+++ b/excel_routes/route_CCE_GIZ_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8651</v>
+        <v>4741</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8891</v>
+        <v>4908</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-240</v>
+        <v>-167</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8651</v>
+        <v>4741</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8891</v>
+        <v>4908</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-240</v>
+        <v>-167</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7552</v>
+        <v>4741</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8285</v>
+        <v>4908</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-733</v>
+        <v>-167</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8651</v>
+        <v>4741</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8891</v>
+        <v>6861</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-240</v>
+        <v>-2120</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12427</v>
+        <v>11686</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13019</v>
+        <v>12467</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-592</v>
+        <v>-781</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-141</t>
+          <t>Air Arabia Egypt E5-585</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11244</v>
+        <v>9409</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11342</v>
+        <v>11783</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-98</v>
+        <v>-2374</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11835</v>
+        <v>10514</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12314</v>
+        <v>11100</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-479</v>
+        <v>-586</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9271</v>
+        <v>11686</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10356</v>
+        <v>12467</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-1085</v>
+        <v>-781</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9637</v>
+        <v>9510</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10821</v>
+        <v>10403</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-1184</v>
+        <v>-893</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9271</v>
+        <v>9176</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9651</v>
+        <v>10403</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-380</v>
+        <v>-1227</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9637</v>
+        <v>8562</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9863</v>
+        <v>9022</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-226</v>
+        <v>-460</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9271</v>
+        <v>9176</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>9863</v>
+        <v>9719</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-592</v>
+        <v>-543</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10116</v>
+        <v>9176</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10356</v>
+        <v>9692</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-240</v>
+        <v>-516</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10624</v>
+        <v>9510</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10821</v>
+        <v>9719</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-197</v>
+        <v>-209</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10116</v>
+        <v>9176</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10356</v>
+        <v>9719</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-240</v>
+        <v>-543</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>10624</v>
+        <v>10012</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10821</v>
+        <v>10403</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-197</v>
+        <v>-391</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9866</v>
+        <v>9176</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15668</v>
+        <v>9719</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5802</v>
+        <v>-543</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10116</v>
+        <v>9176</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15668</v>
+        <v>10403</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-5552</v>
+        <v>-1227</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1328,9 +1328,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Air Arabia Egypt E5-585</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11103</v>
+        <v>9670</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4565</v>
+        <v>-5167</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11103</v>
+        <v>10989</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-4565</v>
+        <v>-3848</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>15</v>
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>11103</v>
+        <v>10989</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4565</v>
+        <v>-3848</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>15</v>
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,17 +1487,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11807</v>
+        <v>10989</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-3861</v>
+        <v>-3848</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>15</v>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>11807</v>
+        <v>11686</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-3861</v>
+        <v>-3151</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>15</v>
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>12371</v>
+        <v>11686</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-3297</v>
+        <v>-3151</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>15</v>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,30 +1622,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>12371</v>
+        <v>10514</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-3297</v>
+        <v>-4323</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,30 +1667,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-141</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>12427</v>
+        <v>11407</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-3241</v>
+        <v>-3430</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12794</v>
+        <v>11686</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2874</v>
+        <v>-3151</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>15</v>
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13216</v>
+        <v>11686</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-2452</v>
+        <v>-3151</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>15</v>
@@ -1792,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,30 +1802,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-585</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9866</v>
+        <v>11825</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-5802</v>
+        <v>-3012</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>11807</v>
+        <v>11825</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-3861</v>
+        <v>-3012</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>15</v>
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>11807</v>
+        <v>11825</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-3861</v>
+        <v>-3012</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>15</v>
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>12794</v>
+        <v>12244</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2874</v>
+        <v>-2593</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>15</v>
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,26 +1982,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>12794</v>
+        <v>12983</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-2874</v>
+        <v>-1854</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2027,30 +2027,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>Air Arabia Egypt E5-585</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>12794</v>
+        <v>9670</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-2874</v>
+        <v>-5167</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2076,13 +2076,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>11807</v>
+        <v>11686</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-3861</v>
+        <v>-3151</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>15</v>
@@ -2107,7 +2107,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2117,30 +2117,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-141</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12427</v>
+        <v>11686</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3241</v>
+        <v>-3151</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2162,17 +2162,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>13075</v>
+        <v>11686</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-2593</v>
+        <v>-3151</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>15</v>
@@ -2197,7 +2197,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05-SEP-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11244</v>
+        <v>12271</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-4424</v>
+        <v>-2566</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>30</v>
@@ -2228,9 +2228,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2252,26 +2252,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11384</v>
+        <v>12271</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>15668</v>
+        <v>12467</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4284</v>
+        <v>-196</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2297,26 +2297,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>11384</v>
+        <v>12271</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15668</v>
+        <v>12467</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-4284</v>
+        <v>-196</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>05-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>10116</v>
+        <v>11100</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-5552</v>
+        <v>-3737</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>30</v>
@@ -2377,7 +2377,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>11384</v>
+        <v>11267</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-4284</v>
+        <v>-3570</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>15</v>
@@ -2422,7 +2422,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2436,13 +2436,13 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>11384</v>
+        <v>11267</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-4284</v>
+        <v>-3570</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>15</v>
@@ -2467,7 +2467,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12-SEP-26</t>
+          <t>10-SEP-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2481,13 +2481,13 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10116</v>
+        <v>10012</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-5552</v>
+        <v>-4825</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2522,30 +2522,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>11807</v>
+        <v>10012</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-3861</v>
+        <v>-4825</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>11807</v>
+        <v>11686</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-3861</v>
+        <v>-3151</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>15</v>
@@ -2602,7 +2602,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>12-SEP-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2612,30 +2612,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-141</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10116</v>
+        <v>11686</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-5552</v>
+        <v>-3151</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2657,30 +2657,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Air Arabia Egypt E5-585</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>11384</v>
+        <v>9670</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-4284</v>
+        <v>-5167</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11384</v>
+        <v>11267</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-4284</v>
+        <v>-3570</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>15</v>
@@ -2737,7 +2737,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2747,30 +2747,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-141</t>
+          <t>flyadeal F3-756</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>10116</v>
+        <v>11267</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-5552</v>
+        <v>-3570</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>15</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>19-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2792,30 +2792,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-754</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>11807</v>
+        <v>10012</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-3861</v>
+        <v>-4825</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2837,30 +2837,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-756</t>
+          <t>Nile Air NP-141</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11807</v>
+        <v>10012</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>15668</v>
+        <v>14837</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-3861</v>
+        <v>-4825</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2882,26 +2882,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-141</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>10116</v>
+        <v>11686</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>10821</v>
+        <v>14837</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-705</v>
+        <v>-3151</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>26-SEP-26</t>
+          <t>19-SEP-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2927,33 +2927,78 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>flyadeal F3-756</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>11686</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>14837</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-3151</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-329</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
           <t>Nile Air NP-141</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>10116</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>10356</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>-240</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
+      <c r="D56" s="2" t="n">
+        <v>10012</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>10403</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-391</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
